--- a/template/default.xlsx
+++ b/template/default.xlsx
@@ -393,52 +393,68 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -628,219 +644,219 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="29.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="2" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="12">
     <mergeCell ref="A1:B6"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="C2:C3"/>
@@ -849,6 +865,10 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
